--- a/artfynd/A 31315-2021 artfynd.xlsx
+++ b/artfynd/A 31315-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31315-2021 artfynd.xlsx
+++ b/artfynd/A 31315-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,62 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>98515094</v>
+        <v>101733208</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>220299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A31315, Högsby, Helgenäs, V Ed, Sm</t>
+          <t>Högsby, Helgenäs, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590307.7244434352</v>
+        <v>590166</v>
       </c>
       <c r="R2" t="n">
-        <v>6429346.719222508</v>
+        <v>6429267</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,22 +748,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-02-07</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-02-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-18</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Vägkanten</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,22 +779,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>98515063</v>
+        <v>98515041</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -835,7 +816,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -848,14 +829,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A31315, Högsby, Helgenäs, V Ed, Sm</t>
+          <t>A 31315, Högsby, Helgenäs, V Ed, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590298.531498089</v>
+        <v>590236</v>
       </c>
       <c r="R3" t="n">
-        <v>6429283.414233964</v>
+        <v>6429359</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,19 +866,9 @@
           <t>2022-02-07</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-02-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,15 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>98515041</v>
+        <v>98515063</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -960,7 +926,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,14 +939,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 31315, Högsby, Helgenäs, V Ed, Sm</t>
+          <t>A31315, Högsby, Helgenäs, V Ed, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590235.7340527156</v>
+        <v>590299</v>
       </c>
       <c r="R4" t="n">
-        <v>6429358.877443211</v>
+        <v>6429283</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,19 +976,9 @@
           <t>2022-02-07</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-02-07</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,6 +1003,116 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>98515094</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>A31315, Högsby, Helgenäs, V Ed, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>590308</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6429347</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Västra Ed</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-02-07</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-02-07</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
